--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/exportTaxGlobal.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/exportTaxGlobal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jinhaochen\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D64FBC8-BA7C-477D-8916-85800A832B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF0F8D7-FBF8-4E7C-8795-237CEEF0B317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,13 +46,15 @@
     <t>美元</t>
   </si>
   <si>
-    <t>当地币折美元汇率</t>
-  </si>
-  <si>
     <t>人民币</t>
   </si>
   <si>
-    <t>人民币折美元汇率</t>
+    <t>当地币折美元</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人民币折美元</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -152,7 +154,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -168,18 +170,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -187,9 +186,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -474,59 +470,59 @@
     <col min="2" max="2" width="31.36328125" customWidth="1"/>
     <col min="3" max="3" width="17.1796875" style="2" customWidth="1"/>
     <col min="4" max="4" width="21.08984375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25" style="6" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
     <col min="9" max="9" width="20.81640625" customWidth="1"/>
     <col min="11" max="11" width="23.453125" customWidth="1"/>
     <col min="13" max="13" width="25.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="9" t="s">
+      <c r="D1" s="9"/>
+      <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="10"/>
-      <c r="G1" s="11" t="s">
+      <c r="F1" s="9"/>
+      <c r="G1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11" t="s">
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="12"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>8</v>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>10</v>
@@ -535,7 +531,7 @@
         <v>6</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>7</v>
@@ -549,20 +545,14 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="J1:M1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:I1"/>
-    <mergeCell ref="J1:M1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576" xr:uid="{7215BDA4-EFB6-482B-B674-E25B704A4B29}">
-      <formula1>0</formula1>
-      <formula2>10000</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>